--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAB28FD-5464-429B-B1DF-BEF5964947DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA22D07-E141-4D2F-881B-F0067A232D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,10 +228,10 @@
     <t>Phase 1 due 4 March</t>
   </si>
   <si>
+    <t>Danh/Eden/Tuyet</t>
+  </si>
+  <si>
     <t>TEST · GCMC Weekly Report</t>
-  </si>
-  <si>
-    <t>Danh Eden Tuyet</t>
   </si>
 </sst>
 </file>
@@ -707,7 +707,7 @@
         <v>60</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>61</v>
@@ -792,7 +792,7 @@
         <v>62</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>11</v>

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA22D07-E141-4D2F-881B-F0067A232D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E006F1D2-D73B-4FCF-9E2F-65C34EA18D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>TEST · GCMC Weekly Report</t>
+  </si>
+  <si>
+    <t>Custom</t>
   </si>
 </sst>
 </file>
@@ -324,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -350,6 +353,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,10 +711,11 @@
     <col min="3" max="3" width="28.21875" style="1" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="62.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="6" max="6" width="14.77734375" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>60</v>
       </c>
@@ -715,8 +728,9 @@
       <c r="D1" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" spans="1:6" ht="43.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -732,8 +746,11 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>49</v>
       </c>
@@ -749,8 +766,9 @@
       <c r="E3" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
@@ -766,8 +784,9 @@
       <c r="E4" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -783,8 +802,9 @@
       <c r="E5" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
@@ -800,8 +820,9 @@
       <c r="E6" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -817,8 +838,9 @@
       <c r="E7" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
@@ -834,11 +856,13 @@
       <c r="E8" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
-    </row>
-    <row r="10" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
@@ -854,8 +878,9 @@
       <c r="E10" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>53</v>
       </c>
@@ -871,8 +896,9 @@
       <c r="E11" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>59</v>
       </c>
@@ -888,8 +914,9 @@
       <c r="E12" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -905,12 +932,14 @@
       <c r="E13" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
@@ -926,8 +955,9 @@
       <c r="E15" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>49</v>
       </c>
@@ -943,6 +973,7 @@
       <c r="E16" s="5" t="s">
         <v>36</v>
       </c>
+      <c r="F16" s="12"/>
     </row>
     <row r="17" spans="1:8" s="5" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -960,6 +991,7 @@
       <c r="E17" s="5" t="s">
         <v>35</v>
       </c>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -977,6 +1009,7 @@
       <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
@@ -994,6 +1027,7 @@
       <c r="E19" s="5" t="s">
         <v>54</v>
       </c>
+      <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1011,9 +1045,11 @@
       <c r="E20" s="5" t="s">
         <v>51</v>
       </c>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9"/>
+      <c r="F21" s="12"/>
     </row>
     <row r="22" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -1031,6 +1067,7 @@
       <c r="E22" s="5" t="s">
         <v>36</v>
       </c>
+      <c r="F22" s="12"/>
     </row>
     <row r="23" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1048,6 +1085,7 @@
       <c r="E23" s="5" t="s">
         <v>35</v>
       </c>
+      <c r="F23" s="12"/>
     </row>
     <row r="24" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
@@ -1065,7 +1103,7 @@
       <c r="E24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="1"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E006F1D2-D73B-4FCF-9E2F-65C34EA18D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEF3A33-1184-403C-B7B2-2007FD6CBD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -234,7 +234,10 @@
     <t>TEST · GCMC Weekly Report</t>
   </si>
   <si>
-    <t>Custom</t>
+    <t>Highlight</t>
+  </si>
+  <si>
+    <t>CustomFX</t>
   </si>
 </sst>
 </file>
@@ -747,7 +750,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -766,7 +769,9 @@
       <c r="E3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEF3A33-1184-403C-B7B2-2007FD6CBD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFF790C-030F-4078-9EAC-8BF643F40ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="68">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -1032,7 +1032,9 @@
       <c r="E19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="12"/>
+      <c r="F19" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFF790C-030F-4078-9EAC-8BF643F40ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CAE4C7-7570-4765-B253-01CEC840782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -718,7 +718,7 @@
     <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>60</v>
       </c>
@@ -733,7 +733,7 @@
       </c>
       <c r="F1" s="10"/>
     </row>
-    <row r="2" spans="1:6" ht="43.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="43.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -753,7 +753,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>49</v>
       </c>
@@ -769,11 +769,11 @@
       <c r="E3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
@@ -791,7 +791,7 @@
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -809,7 +809,7 @@
       </c>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
@@ -827,7 +827,7 @@
       </c>
       <c r="F6" s="12"/>
     </row>
-    <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -845,7 +845,7 @@
       </c>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
@@ -863,11 +863,11 @@
       </c>
       <c r="F8" s="12"/>
     </row>
-    <row r="9" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
@@ -885,7 +885,7 @@
       </c>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>53</v>
       </c>
@@ -903,7 +903,7 @@
       </c>
       <c r="F11" s="12"/>
     </row>
-    <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>59</v>
       </c>
@@ -921,7 +921,7 @@
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -939,12 +939,12 @@
       </c>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
@@ -962,7 +962,7 @@
       </c>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>49</v>
       </c>
@@ -1032,9 +1032,7 @@
       <c r="E19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>66</v>
-      </c>
+      <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CAE4C7-7570-4765-B253-01CEC840782D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A44B15-07C5-4179-BB49-B479B9555E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -718,7 +718,7 @@
     <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>60</v>
       </c>
@@ -733,7 +733,7 @@
       </c>
       <c r="F1" s="10"/>
     </row>
-    <row r="2" spans="1:7" ht="43.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="43.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -753,7 +753,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>49</v>
       </c>
@@ -769,11 +769,8 @@
       <c r="E3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
@@ -791,7 +788,7 @@
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row r="5" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -807,9 +804,11 @@
       <c r="E5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
@@ -827,7 +826,7 @@
       </c>
       <c r="F6" s="12"/>
     </row>
-    <row r="7" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -845,7 +844,7 @@
       </c>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>59</v>
       </c>
@@ -863,11 +862,11 @@
       </c>
       <c r="F8" s="12"/>
     </row>
-    <row r="9" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
@@ -885,7 +884,7 @@
       </c>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>53</v>
       </c>
@@ -903,7 +902,7 @@
       </c>
       <c r="F11" s="12"/>
     </row>
-    <row r="12" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>59</v>
       </c>
@@ -921,7 +920,7 @@
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -939,12 +938,12 @@
       </c>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="9"/>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
@@ -962,7 +961,7 @@
       </c>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:7" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>49</v>
       </c>

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A44B15-07C5-4179-BB49-B479B9555E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE05C940-4FB1-4404-8C08-27BB70A36CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>CustomFX</t>
+  </si>
+  <si>
+    <t>Alumni Valentine / New year assets 2</t>
   </si>
 </sst>
 </file>
@@ -706,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.5546875" style="1" customWidth="1"/>
@@ -1167,6 +1170,23 @@
         <v>36</v>
       </c>
     </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E23">
     <sortCondition ref="C3:C23"/>
@@ -1177,7 +1197,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{E5BFD1E3-D60A-48B7-887F-264F651EBB2F}">
       <formula1>"Very Light,Light,Medium,Med-High,High,Overloaded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D28" xr:uid="{57C0FF5B-A281-498F-B368-FFF48C59A553}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D29" xr:uid="{57C0FF5B-A281-498F-B368-FFF48C59A553}">
       <formula1>"To Do,In Progress,In Review,Done,On-hold"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE05C940-4FB1-4404-8C08-27BB70A36CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD4D756-0545-43A0-9A8C-F1D2230558CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="67">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Due EO Feb 2026</t>
   </si>
   <si>
-    <t>SR H1 Update (edit) Vietnam video</t>
-  </si>
-  <si>
     <t>Lunar New Year eDM GIF</t>
   </si>
   <si>
@@ -114,9 +111,6 @@
     <t>RMIT Trades Event - maps and design assets</t>
   </si>
   <si>
-    <t>COP video endframe update</t>
-  </si>
-  <si>
     <t>Eid al Fitr 2026 eDM</t>
   </si>
   <si>
@@ -129,60 +123,18 @@
     <t>RMIT Trades Event</t>
   </si>
   <si>
-    <t>In progress, due 6 Feb</t>
-  </si>
-  <si>
-    <t>Done, FA/WF sent 30 Jan</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>In progress, some assets pending (waiting for info)</t>
-  </si>
-  <si>
     <t>Due 10 Feb</t>
   </si>
   <si>
-    <t>Due 9 Feb</t>
-  </si>
-  <si>
-    <t>Revision in progress, due 6 Feb</t>
-  </si>
-  <si>
     <t>Uni acronym challenge</t>
   </si>
   <si>
     <t>Awaiting approval / review, due 6 Feb</t>
   </si>
   <si>
-    <t>H1 2026 China Always On - videos</t>
-  </si>
-  <si>
-    <t>H1 2026 China Always On - Static x5</t>
-  </si>
-  <si>
-    <t>Tuyet</t>
-  </si>
-  <si>
-    <t>Updated on Feb 2, waiting approval</t>
-  </si>
-  <si>
-    <t>Final revision in progress</t>
-  </si>
-  <si>
-    <t>H1 Domestic</t>
-  </si>
-  <si>
-    <t>INTON New year assets</t>
-  </si>
-  <si>
-    <t>INTON Valentine assets</t>
-  </si>
-  <si>
-    <t>Alumni Valentine / New year assets</t>
-  </si>
-  <si>
     <t>INTON Holidays assets</t>
   </si>
   <si>
@@ -192,33 +144,15 @@
     <t>Updated on 2 Feb</t>
   </si>
   <si>
-    <t>Short-form video endframe update #2</t>
-  </si>
-  <si>
-    <t>H1 / H2 COP</t>
-  </si>
-  <si>
-    <t>Updated on 27 Jan</t>
-  </si>
-  <si>
-    <t>Updated on 2 Feb, due 6 Feb</t>
-  </si>
-  <si>
     <t>H1 2026 INTON Always On</t>
   </si>
   <si>
     <t>H1 2026 Indonesia Always On – META &amp; TIKTOK</t>
   </si>
   <si>
-    <t>Approved on 2 Feb</t>
-  </si>
-  <si>
     <t>Comms Holdays assets</t>
   </si>
   <si>
-    <t xml:space="preserve"> | 3 Feb - 10 Feb 2026</t>
-  </si>
-  <si>
     <t>Last updated 10 Feb, 03:10 ICT</t>
   </si>
   <si>
@@ -234,13 +168,73 @@
     <t>TEST · GCMC Weekly Report</t>
   </si>
   <si>
-    <t>Highlight</t>
-  </si>
-  <si>
     <t>CustomFX</t>
   </si>
   <si>
-    <t>Alumni Valentine / New year assets 2</t>
+    <t>FA/WF sent 7 Feb</t>
+  </si>
+  <si>
+    <t>Even passed before final revision</t>
+  </si>
+  <si>
+    <t>2026 INTON Event style guide</t>
+  </si>
+  <si>
+    <t>Danh/Trinh/Tran</t>
+  </si>
+  <si>
+    <t>In progress, due 25 Feb</t>
+  </si>
+  <si>
+    <t>Danh/Trinh/Tran/Tuyet</t>
+  </si>
+  <si>
+    <t>All assets sent 9 Feb, in review</t>
+  </si>
+  <si>
+    <t>Domestic Always On 2026</t>
+  </si>
+  <si>
+    <t>Concept selection in progress</t>
+  </si>
+  <si>
+    <t>Map asset done, waiting for printed assets info</t>
+  </si>
+  <si>
+    <t>2/6 assets done. The rest pending for more info</t>
+  </si>
+  <si>
+    <t>2026 INTON Open Days</t>
+  </si>
+  <si>
+    <t>H1 Sem 2</t>
+  </si>
+  <si>
+    <t>H1 Domestic Always On</t>
+  </si>
+  <si>
+    <t>Updated on 5 Feb, waiting for review</t>
+  </si>
+  <si>
+    <t>1st draft sent 9 Feb</t>
+  </si>
+  <si>
+    <t>India Always On 2026 – PMAX creative asset</t>
+  </si>
+  <si>
+    <t>Trinh/Tuyet</t>
+  </si>
+  <si>
+    <t>Due 13 Feb for static and 27 Feb for videos</t>
+  </si>
+  <si>
+    <t>Updated on Feb 6</t>
+  </si>
+  <si>
+    <t>H1 2026 China Always On - WECHAT &amp; RED</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> · 3 Feb - 10 Feb 2026</t>
   </si>
 </sst>
 </file>
@@ -709,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.5546875" style="1" customWidth="1"/>
@@ -723,16 +717,16 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F1" s="10"/>
     </row>
@@ -753,41 +747,41 @@
         <v>4</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>19</v>
+        <v>56</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -795,45 +789,43 @@
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>66</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -849,19 +841,19 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>20</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -871,10 +863,10 @@
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>10</v>
@@ -883,34 +875,34 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>26</v>
+        <v>58</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>27</v>
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>10</v>
@@ -919,7 +911,7 @@
         <v>12</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" s="12"/>
     </row>
@@ -927,17 +919,17 @@
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>29</v>
+      <c r="B13" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -948,10 +940,10 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>22</v>
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>7</v>
@@ -960,43 +952,43 @@
         <v>5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="5" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>46</v>
+        <v>36</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="1:8" s="5" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>57</v>
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F17" s="12"/>
     </row>
@@ -1004,8 +996,8 @@
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>24</v>
+      <c r="B18" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>7</v>
@@ -1014,56 +1006,58 @@
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F18" s="12"/>
     </row>
     <row r="19" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>54</v>
-      </c>
+      <c r="B19" s="9"/>
       <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="9"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>47</v>
+      <c r="B22" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>9</v>
@@ -1072,124 +1066,34 @@
         <v>12</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>40</v>
+      <c r="B23" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="9"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>36</v>
-      </c>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B24" s="9"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E23">
-    <sortCondition ref="C3:C23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E20">
+    <sortCondition ref="C3:C20"/>
   </sortState>
   <dataConsolidate/>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1197,7 +1101,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{E5BFD1E3-D60A-48B7-887F-264F651EBB2F}">
       <formula1>"Very Light,Light,Medium,Med-High,High,Overloaded"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D29" xr:uid="{57C0FF5B-A281-498F-B368-FFF48C59A553}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D24" xr:uid="{57C0FF5B-A281-498F-B368-FFF48C59A553}">
       <formula1>"To Do,In Progress,In Review,Done,On-hold"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD4D756-0545-43A0-9A8C-F1D2230558CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C324CF-563A-4DD5-B589-706ACBA94C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,9 +165,6 @@
     <t>Danh/Eden/Tuyet</t>
   </si>
   <si>
-    <t>TEST · GCMC Weekly Report</t>
-  </si>
-  <si>
     <t>CustomFX</t>
   </si>
   <si>
@@ -235,6 +232,9 @@
   </si>
   <si>
     <t xml:space="preserve"> · 3 Feb - 10 Feb 2026</t>
+  </si>
+  <si>
+    <t>GCMC Weekly Report</t>
   </si>
 </sst>
 </file>
@@ -717,10 +717,10 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>39</v>
@@ -747,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -758,30 +758,30 @@
         <v>34</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -799,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>40</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>17</v>
@@ -853,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -875,16 +875,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" s="12"/>
     </row>
@@ -929,7 +929,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -952,7 +952,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="12"/>
     </row>
@@ -970,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" s="12"/>
     </row>
@@ -1019,10 +1019,10 @@
         <v>36</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>12</v>
@@ -1046,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="1"/>
@@ -1074,16 +1074,16 @@
         <v>36</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C324CF-563A-4DD5-B589-706ACBA94C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A677E22-314B-4AE0-8CB8-B7AE0182C35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,9 +147,6 @@
     <t>H1 2026 INTON Always On</t>
   </si>
   <si>
-    <t>H1 2026 Indonesia Always On – META &amp; TIKTOK</t>
-  </si>
-  <si>
     <t>Comms Holdays assets</t>
   </si>
   <si>
@@ -228,13 +225,16 @@
     <t>Updated on Feb 6</t>
   </si>
   <si>
-    <t>H1 2026 China Always On - WECHAT &amp; RED</t>
-  </si>
-  <si>
     <t xml:space="preserve"> · 3 Feb - 10 Feb 2026</t>
   </si>
   <si>
     <t>GCMC Weekly Report</t>
+  </si>
+  <si>
+    <t>China Always On - WECHAT &amp; RED</t>
+  </si>
+  <si>
+    <t>Indonesia Always On – META &amp; TIKTOK</t>
   </si>
 </sst>
 </file>
@@ -717,13 +717,13 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>29</v>
@@ -747,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -758,30 +758,30 @@
         <v>34</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -799,31 +799,31 @@
         <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>17</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>19</v>
@@ -853,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -875,16 +875,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
@@ -893,13 +893,13 @@
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>25</v>
@@ -929,7 +929,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -940,7 +940,7 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
@@ -952,7 +952,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="12"/>
     </row>
@@ -961,7 +961,7 @@
         <v>36</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
@@ -970,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="12"/>
     </row>
@@ -1019,10 +1019,10 @@
         <v>36</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>12</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>20</v>
@@ -1046,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="1"/>
@@ -1074,16 +1074,16 @@
         <v>36</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A677E22-314B-4AE0-8CB8-B7AE0182C35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2653DCE-29F6-4FE6-A868-3C1304D6DF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,9 +126,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>Due 10 Feb</t>
-  </si>
-  <si>
     <t>Uni acronym challenge</t>
   </si>
   <si>
@@ -168,9 +165,6 @@
     <t>FA/WF sent 7 Feb</t>
   </si>
   <si>
-    <t>Even passed before final revision</t>
-  </si>
-  <si>
     <t>2026 INTON Event style guide</t>
   </si>
   <si>
@@ -235,6 +229,12 @@
   </si>
   <si>
     <t>Indonesia Always On – META &amp; TIKTOK</t>
+  </si>
+  <si>
+    <t>Concept selection Due 10 Feb</t>
+  </si>
+  <si>
+    <t>Event passed before final revision</t>
   </si>
 </sst>
 </file>
@@ -717,13 +717,13 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>29</v>
@@ -747,41 +747,41 @@
         <v>4</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -799,31 +799,31 @@
         <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>17</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>19</v>
@@ -853,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -875,16 +875,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
@@ -893,13 +893,13 @@
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>25</v>
@@ -929,7 +929,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -940,7 +940,7 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
@@ -952,16 +952,16 @@
         <v>5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" s="5" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
@@ -970,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F16" s="12"/>
     </row>
@@ -1006,7 +1006,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F18" s="12"/>
     </row>
@@ -1016,25 +1016,25 @@
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>20</v>
@@ -1046,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="1"/>
@@ -1057,7 +1057,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>9</v>
@@ -1066,24 +1066,24 @@
         <v>12</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2653DCE-29F6-4FE6-A868-3C1304D6DF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B9DEFF-2827-46E4-B466-6AC894B23637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -127,9 +127,6 @@
   </si>
   <si>
     <t>Uni acronym challenge</t>
-  </si>
-  <si>
-    <t>Awaiting approval / review, due 6 Feb</t>
   </si>
   <si>
     <t>INTON Holidays assets</t>
@@ -717,13 +714,13 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="C1" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>29</v>
@@ -747,41 +744,41 @@
         <v>4</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -799,31 +796,31 @@
         <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>17</v>
@@ -841,7 +838,7 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>19</v>
@@ -853,7 +850,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -875,16 +872,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
@@ -893,13 +890,13 @@
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>25</v>
@@ -929,7 +926,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -940,7 +937,7 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
@@ -952,16 +949,16 @@
         <v>5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" s="5" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
@@ -970,7 +967,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" s="12"/>
     </row>
@@ -1006,7 +1003,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" s="12"/>
     </row>
@@ -1016,25 +1013,25 @@
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>20</v>
@@ -1046,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="1"/>
@@ -1065,25 +1062,23 @@
       <c r="D22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">

--- a/data/reports/W06_2026.xlsx
+++ b/data/reports/W06_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B9DEFF-2827-46E4-B466-6AC894B23637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808C4AD3-338F-4FCB-932E-941DCED23879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>All assets updated on 19 Jan</t>
   </si>
   <si>
-    <t>x4 Aussie and international snacks reaction videos</t>
-  </si>
-  <si>
     <t>RMIT Trades Event - maps and design assets</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>Uni acronym challenge</t>
-  </si>
-  <si>
     <t>INTON Holidays assets</t>
   </si>
   <si>
@@ -232,6 +226,12 @@
   </si>
   <si>
     <t>Event passed before final revision</t>
+  </si>
+  <si>
+    <t>Uni acronym challenge videos</t>
+  </si>
+  <si>
+    <t>Aussie and international snacks reaction videos</t>
   </si>
 </sst>
 </file>
@@ -714,16 +714,16 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="52.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F1" s="10"/>
     </row>
@@ -744,41 +744,41 @@
         <v>4</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -796,31 +796,31 @@
         <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>17</v>
@@ -838,7 +838,7 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>19</v>
@@ -850,7 +850,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -860,10 +860,10 @@
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>10</v>
@@ -872,16 +872,16 @@
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
@@ -890,16 +890,16 @@
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>10</v>
@@ -908,7 +908,7 @@
         <v>12</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="12"/>
     </row>
@@ -917,7 +917,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>10</v>
@@ -926,7 +926,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F13" s="12"/>
     </row>
@@ -937,7 +937,7 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
@@ -949,16 +949,16 @@
         <v>5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" s="5" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
@@ -967,7 +967,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16" s="12"/>
     </row>
@@ -976,7 +976,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>7</v>
@@ -1003,7 +1003,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F18" s="12"/>
     </row>
@@ -1013,25 +1013,25 @@
     </row>
     <row r="20" spans="1:8" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F20" s="12"/>
     </row>
     <row r="21" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>20</v>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="1"/>
@@ -1054,7 +1054,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>9</v>
@@ -1066,19 +1066,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
